--- a/branches/migration/2026.0.0-template-v0.13.1/CodeSystem-mii-cs-meta-diz-standorte.xlsx
+++ b/branches/migration/2026.0.0-template-v0.13.1/CodeSystem-mii-cs-meta-diz-standorte.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-18</t>
+    <t>2026-09-01</t>
   </si>
   <si>
     <t>Publisher</t>
